--- a/qa/entrega-1/Matriz_Riesgos_PanelOrganizador_CIN421.xlsx
+++ b/qa/entrega-1/Matriz_Riesgos_PanelOrganizador_CIN421.xlsx
@@ -1405,7 +1405,7 @@
     <row r="1" ht="19.5" customHeight="1" s="35">
       <c r="A1" s="58" t="inlineStr">
         <is>
-          <t>Registro de riesgos · Panel Organizador · Grupo QA</t>
+          <t>Registro de riesgos · Panel Organizador · Grupo 7</t>
         </is>
       </c>
     </row>
